--- a/VerveStacks_LVA/vt_vervestacks_LVA_v1.xlsx
+++ b/VerveStacks_LVA/vt_vervestacks_LVA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49282F90-DAD2-4525-922C-0850CD5D1CF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6B173B9-CD0C-46A3-8F5A-E9F12734AFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2BF06560-578C-4EAA-BA9D-E4313488ECB8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EB64B604-21E6-4745-8850-E6F9E7997A07}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -712,7 +712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C698223B-8C84-4510-BF19-763E5F4A41FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4B82FCA-D5E2-4B70-9B9C-C7EACBAF02AB}">
   <dimension ref="B9:T15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1066,7 +1066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A3CDECA-4588-4DC5-9416-D113A0CE32ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7522CE27-A77C-4A75-80C0-700BFCDB1825}">
   <dimension ref="B9:T17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1532,7 +1532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1E7C90B-C3B9-484F-96A1-C171262A4E82}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90727BC5-1A1E-43D4-81A8-FF9ED9CA0ED3}">
   <dimension ref="B9:T34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2503,7 +2503,7 @@
         <v>39</v>
       </c>
       <c r="P28" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="Q28" t="s">
         <v>55</v>
@@ -2559,7 +2559,7 @@
         <v>39</v>
       </c>
       <c r="P29" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q29" t="s">
         <v>55</v>
@@ -2615,7 +2615,7 @@
         <v>41</v>
       </c>
       <c r="P30" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q30" t="s">
         <v>55</v>
@@ -2671,7 +2671,7 @@
         <v>41</v>
       </c>
       <c r="P31" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="Q31" t="s">
         <v>55</v>
@@ -2818,7 +2818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A37F58FC-6749-4235-AED5-3EDFF0BD3773}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{059A8900-CD42-4960-8998-A6FDC4C7B4A1}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_LVA/vt_vervestacks_LVA_v1.xlsx
+++ b/VerveStacks_LVA/vt_vervestacks_LVA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6B173B9-CD0C-46A3-8F5A-E9F12734AFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F3FBA6E-E6B3-49BB-994B-FCCF610AA1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EB64B604-21E6-4745-8850-E6F9E7997A07}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C3AB6E6B-A14B-4304-990C-1689110C5156}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -712,7 +712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4B82FCA-D5E2-4B70-9B9C-C7EACBAF02AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4488D11B-9238-4F00-B77F-F2B08222C812}">
   <dimension ref="B9:T15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1066,7 +1066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7522CE27-A77C-4A75-80C0-700BFCDB1825}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3592E705-A28B-4C26-B70C-35FFFD514AA8}">
   <dimension ref="B9:T17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1532,7 +1532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90727BC5-1A1E-43D4-81A8-FF9ED9CA0ED3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DCCE801-CA15-4485-8369-6309439841C7}">
   <dimension ref="B9:T34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2818,7 +2818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{059A8900-CD42-4960-8998-A6FDC4C7B4A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE5FD68-6578-438C-8B48-91D54D95F9E2}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_LVA/vt_vervestacks_LVA_v1.xlsx
+++ b/VerveStacks_LVA/vt_vervestacks_LVA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F3FBA6E-E6B3-49BB-994B-FCCF610AA1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA227634-1B07-4858-B9B9-78DD978E51A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C3AB6E6B-A14B-4304-990C-1689110C5156}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9718C677-BE25-4869-B0B7-C378AAB08E46}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -712,7 +712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4488D11B-9238-4F00-B77F-F2B08222C812}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D89F7D0-9384-4E81-B494-DFEBDD795EC1}">
   <dimension ref="B9:T15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -791,7 +791,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.28982625000000001</v>
+        <v>0.20287837500000003</v>
       </c>
       <c r="F11">
         <v>1365</v>
@@ -847,7 +847,7 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.450625</v>
+        <v>0.31543749999999998</v>
       </c>
       <c r="F12">
         <v>1365</v>
@@ -903,7 +903,7 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0.46865000000000007</v>
+        <v>0.32805500000000004</v>
       </c>
       <c r="F13">
         <v>1365</v>
@@ -959,7 +959,7 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.49118125000000001</v>
+        <v>0.34382687499999998</v>
       </c>
       <c r="F14">
         <v>1365</v>
@@ -1015,7 +1015,7 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.522725</v>
+        <v>0.36590749999999994</v>
       </c>
       <c r="F15">
         <v>1365</v>
@@ -1066,7 +1066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3592E705-A28B-4C26-B70C-35FFFD514AA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E989DA3-D23A-4B7D-A173-1E502069E15C}">
   <dimension ref="B9:T17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1532,7 +1532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DCCE801-CA15-4485-8369-6309439841C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73795D32-C06D-4DAD-B1B1-91A16BD68298}">
   <dimension ref="B9:T34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1670,7 +1670,7 @@
         <v>3.0000000000001137E-3</v>
       </c>
       <c r="G12">
-        <v>0.33123000000000002</v>
+        <v>0.23186100000000001</v>
       </c>
       <c r="N12" t="s">
         <v>53</v>
@@ -1711,7 +1711,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="G13">
-        <v>0.51500000000000001</v>
+        <v>0.36049999999999999</v>
       </c>
       <c r="H13">
         <v>1485.0000000000002</v>
@@ -1764,7 +1764,7 @@
         <v>0.158</v>
       </c>
       <c r="G14">
-        <v>0.53560000000000008</v>
+        <v>0.37492000000000003</v>
       </c>
       <c r="H14">
         <v>1265</v>
@@ -1817,7 +1817,7 @@
         <v>0.441</v>
       </c>
       <c r="G15">
-        <v>0.56135000000000002</v>
+        <v>0.39294499999999999</v>
       </c>
       <c r="H15">
         <v>1100</v>
@@ -1870,7 +1870,7 @@
         <v>0.44</v>
       </c>
       <c r="G16">
-        <v>0.59740000000000004</v>
+        <v>0.41817999999999994</v>
       </c>
       <c r="H16">
         <v>1100</v>
@@ -2503,7 +2503,7 @@
         <v>39</v>
       </c>
       <c r="P28" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q28" t="s">
         <v>55</v>
@@ -2559,7 +2559,7 @@
         <v>39</v>
       </c>
       <c r="P29" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="Q29" t="s">
         <v>55</v>
@@ -2818,7 +2818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE5FD68-6578-438C-8B48-91D54D95F9E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D0E005-54E7-4F6D-8ACE-CD7648067D0D}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_LVA/vt_vervestacks_LVA_v1.xlsx
+++ b/VerveStacks_LVA/vt_vervestacks_LVA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA227634-1B07-4858-B9B9-78DD978E51A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{113CD0BB-C3BF-449F-859D-C846EE8635BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9718C677-BE25-4869-B0B7-C378AAB08E46}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B04F1F48-85F7-4457-A23C-47214FE84859}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -712,7 +712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D89F7D0-9384-4E81-B494-DFEBDD795EC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FABC7F27-9AA0-41BB-95FC-81CA63A7721B}">
   <dimension ref="B9:T15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1066,7 +1066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E989DA3-D23A-4B7D-A173-1E502069E15C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C9F4DC2-798F-4D03-A674-311D85462044}">
   <dimension ref="B9:T17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1532,7 +1532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73795D32-C06D-4DAD-B1B1-91A16BD68298}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD769F1-7C5A-4853-B923-FCB3E259C580}">
   <dimension ref="B9:T34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2615,7 +2615,7 @@
         <v>41</v>
       </c>
       <c r="P30" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="Q30" t="s">
         <v>55</v>
@@ -2671,7 +2671,7 @@
         <v>41</v>
       </c>
       <c r="P31" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q31" t="s">
         <v>55</v>
@@ -2818,7 +2818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D0E005-54E7-4F6D-8ACE-CD7648067D0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{109CCD98-EA53-4CCB-BBDE-7741DB662FAA}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_LVA/vt_vervestacks_LVA_v1.xlsx
+++ b/VerveStacks_LVA/vt_vervestacks_LVA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{113CD0BB-C3BF-449F-859D-C846EE8635BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BD10D76-1646-4F8F-B9B2-78FBF4D869E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B04F1F48-85F7-4457-A23C-47214FE84859}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{08F43B41-A4A4-4408-941C-AA28B189D482}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -712,7 +712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FABC7F27-9AA0-41BB-95FC-81CA63A7721B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB1BB4EB-5383-45FB-8FF8-FCF283E9D635}">
   <dimension ref="B9:T15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1066,7 +1066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C9F4DC2-798F-4D03-A674-311D85462044}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCACED48-5521-4FF4-BE28-C7AC1AE87D28}">
   <dimension ref="B9:T17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1532,7 +1532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CD769F1-7C5A-4853-B923-FCB3E259C580}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6E212F-D66B-4110-8521-B70422BD4170}">
   <dimension ref="B9:T34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2503,7 +2503,7 @@
         <v>39</v>
       </c>
       <c r="P28" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="Q28" t="s">
         <v>55</v>
@@ -2559,7 +2559,7 @@
         <v>39</v>
       </c>
       <c r="P29" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q29" t="s">
         <v>55</v>
@@ -2615,7 +2615,7 @@
         <v>41</v>
       </c>
       <c r="P30" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q30" t="s">
         <v>55</v>
@@ -2671,7 +2671,7 @@
         <v>41</v>
       </c>
       <c r="P31" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="Q31" t="s">
         <v>55</v>
@@ -2818,7 +2818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{109CCD98-EA53-4CCB-BBDE-7741DB662FAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3F9507-50F7-47F6-B5A1-46A41A181B72}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_LVA/vt_vervestacks_LVA_v1.xlsx
+++ b/VerveStacks_LVA/vt_vervestacks_LVA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_LVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BD10D76-1646-4F8F-B9B2-78FBF4D869E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0C9E13A-9EDC-4E0C-B7F6-8BC4F934D166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{08F43B41-A4A4-4408-941C-AA28B189D482}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5C2EBDAB-B3B0-4FD5-B104-A31A9F623BA3}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -712,7 +712,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB1BB4EB-5383-45FB-8FF8-FCF283E9D635}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA4786D9-7695-4CB8-B481-70729B06D5DF}">
   <dimension ref="B9:T15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1066,7 +1066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCACED48-5521-4FF4-BE28-C7AC1AE87D28}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C6A3765-A10C-4B92-A852-67BC25E435B2}">
   <dimension ref="B9:T17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1532,7 +1532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6E212F-D66B-4110-8521-B70422BD4170}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94F1FF74-2F39-4356-8989-8CD28C86695F}">
   <dimension ref="B9:T34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2126,7 +2126,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L21">
-        <v>0.14444285101303503</v>
+        <v>0.14444285101303506</v>
       </c>
       <c r="N21" t="s">
         <v>53</v>
@@ -2170,7 +2170,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L22">
-        <v>0.14444285101303503</v>
+        <v>0.14444285101303506</v>
       </c>
       <c r="N22" t="s">
         <v>53</v>
@@ -2214,7 +2214,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L23">
-        <v>0.14444285101303503</v>
+        <v>0.14444285101303506</v>
       </c>
       <c r="N23" t="s">
         <v>53</v>
@@ -2503,7 +2503,7 @@
         <v>39</v>
       </c>
       <c r="P28" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q28" t="s">
         <v>55</v>
@@ -2559,7 +2559,7 @@
         <v>39</v>
       </c>
       <c r="P29" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="Q29" t="s">
         <v>55</v>
@@ -2615,7 +2615,7 @@
         <v>41</v>
       </c>
       <c r="P30" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="Q30" t="s">
         <v>55</v>
@@ -2671,7 +2671,7 @@
         <v>41</v>
       </c>
       <c r="P31" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="Q31" t="s">
         <v>55</v>
@@ -2818,7 +2818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD3F9507-50F7-47F6-B5A1-46A41A181B72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7755ACF-D3CA-4552-A5D0-B17F430102A1}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
